--- a/data/trans_dic/AIRE_1_R-Clase-trans_dic.xlsx
+++ b/data/trans_dic/AIRE_1_R-Clase-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -489,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que no está dispuesta a pagar para reducir la contaminación del aire (impuesto durante 5 años)</t>
+          <t>Población que no está dispuesta a pagar para reducir la contaminación del aire (impuesto durante 5 años) (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -571,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>45,41; 68,63</t>
+          <t>47,22; 67,9</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>57,75; 76,88</t>
+          <t>58,22; 77,0</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>56,32; 70,68</t>
+          <t>55,93; 70,58</t>
         </is>
       </c>
     </row>
@@ -621,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>63,51; 83,95</t>
+          <t>65,46; 84,53</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>60,58; 83,11</t>
+          <t>61,43; 83,53</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>66,92; 82,07</t>
+          <t>67,15; 81,71</t>
         </is>
       </c>
     </row>
@@ -671,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>58,78; 86,87</t>
+          <t>60,88; 87,55</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>60,77; 86,28</t>
+          <t>59,67; 86,63</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>64,44; 83,25</t>
+          <t>64,28; 83,59</t>
         </is>
       </c>
     </row>
@@ -721,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>76,09; 92,03</t>
+          <t>75,63; 92,41</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>57,59; 77,82</t>
+          <t>58,08; 78,61</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>70,2; 84,9</t>
+          <t>69,77; 84,66</t>
         </is>
       </c>
     </row>
@@ -771,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>72,76; 91,03</t>
+          <t>72,01; 90,24</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>68,19; 85,97</t>
+          <t>68,45; 87,25</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>73,35; 86,05</t>
+          <t>72,68; 86,1</t>
         </is>
       </c>
     </row>
@@ -821,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>60,44; 87,39</t>
+          <t>60,76; 87,15</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>66,39; 90,26</t>
+          <t>66,48; 89,93</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>69,14; 86,76</t>
+          <t>69,28; 86,49</t>
         </is>
       </c>
     </row>
@@ -871,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>72,2; 82,86</t>
+          <t>72,01; 83,02</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>68,3; 77,16</t>
+          <t>68,6; 77,5</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>71,78; 78,53</t>
+          <t>71,2; 78,54</t>
         </is>
       </c>
     </row>
@@ -905,4 +906,602 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Población que no está dispuesta a pagar para reducir la contaminación del aire (impuesto durante 5 años) (tasa de respuesta: 100,0%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Grupo I y II</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>111</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>31097</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>49285</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>80383</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>25541; 36726</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>42226; 55849</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>70811; 89367</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Grupo III</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>103</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>36702</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>35968</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>72670</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>31707; 40947</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>29950; 40726</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>65263; 79413</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Grupo IV y V</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>18275</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>28542</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>46818</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>14894; 21417</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>22710; 32970</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>40192; 52267</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Grupo VI</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>106</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>216</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>100610</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>74234</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>174844</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>90879; 111043</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>61508; 83244</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>157716; 191387</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Grupo VII</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>143</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>41519</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>58385</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>99904</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>36181; 45339</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>50952; 64945</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>90622; 107353</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>No ha trabajado</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n"/>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>23466</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>32283</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>55749</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>18770; 26924</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>26744; 36179</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>49276; 61515</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>343</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>368</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>711</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>251670</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>278698</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>530367</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>236389; 272541</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>260634; 294445</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>504212; 556195</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A19:A21"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/AIRE_1_R-Clase-trans_dic.xlsx
+++ b/data/trans_dic/AIRE_1_R-Clase-trans_dic.xlsx
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>47,22; 67,9</t>
+          <t>46,53; 67,54</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>58,22; 77,0</t>
+          <t>57,81; 77,32</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>55,93; 70,58</t>
+          <t>55,71; 70,1</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>65,46; 84,53</t>
+          <t>65,22; 84,53</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>61,43; 83,53</t>
+          <t>62,79; 83,42</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>67,15; 81,71</t>
+          <t>67,24; 81,4</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>60,88; 87,55</t>
+          <t>60,4; 87,13</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>59,67; 86,63</t>
+          <t>59,44; 86,18</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>64,28; 83,59</t>
+          <t>64,82; 83,61</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>75,63; 92,41</t>
+          <t>75,73; 92,38</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>58,08; 78,61</t>
+          <t>58,06; 78,57</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>69,77; 84,66</t>
+          <t>70,0; 85,13</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>72,01; 90,24</t>
+          <t>72,15; 89,8</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>68,45; 87,25</t>
+          <t>68,61; 86,35</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>72,68; 86,1</t>
+          <t>72,91; 85,45</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>60,76; 87,15</t>
+          <t>61,57; 87,38</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>66,48; 89,93</t>
+          <t>66,51; 89,85</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>69,28; 86,49</t>
+          <t>68,23; 85,36</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>72,01; 83,02</t>
+          <t>72,17; 82,04</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>68,6; 77,5</t>
+          <t>68,38; 77,25</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>71,2; 78,54</t>
+          <t>71,54; 78,44</t>
         </is>
       </c>
     </row>
@@ -1032,17 +1032,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>25541; 36726</t>
+          <t>25168; 36533</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>42226; 55849</t>
+          <t>41930; 56082</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>70811; 89367</t>
+          <t>70533; 88755</t>
         </is>
       </c>
     </row>
@@ -1105,17 +1105,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>31707; 40947</t>
+          <t>31591; 40946</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>29950; 40726</t>
+          <t>30614; 40672</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>65263; 79413</t>
+          <t>65350; 79119</t>
         </is>
       </c>
     </row>
@@ -1178,17 +1178,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>14894; 21417</t>
+          <t>14776; 21316</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>22710; 32970</t>
+          <t>22623; 32798</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>40192; 52267</t>
+          <t>40525; 52275</t>
         </is>
       </c>
     </row>
@@ -1251,17 +1251,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>90879; 111043</t>
+          <t>91000; 111003</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>61508; 83244</t>
+          <t>61482; 83199</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>157716; 191387</t>
+          <t>158244; 192435</t>
         </is>
       </c>
     </row>
@@ -1324,17 +1324,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>36181; 45339</t>
+          <t>36248; 45120</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>50952; 64945</t>
+          <t>51069; 64282</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>90622; 107353</t>
+          <t>90906; 106540</t>
         </is>
       </c>
     </row>
@@ -1397,17 +1397,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>18770; 26924</t>
+          <t>19021; 26994</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>26744; 36179</t>
+          <t>26758; 36145</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>49276; 61515</t>
+          <t>48530; 60707</t>
         </is>
       </c>
     </row>
@@ -1470,17 +1470,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>236389; 272541</t>
+          <t>236932; 269341</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>260634; 294445</t>
+          <t>259784; 293464</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>504212; 556195</t>
+          <t>506638; 555525</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/AIRE_1_R-Clase-trans_dic.xlsx
+++ b/data/trans_dic/AIRE_1_R-Clase-trans_dic.xlsx
@@ -496,12 +496,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>57,49%</t>
+          <t>67,27%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>67,95%</t>
+          <t>56,79%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>63,49%</t>
+          <t>62,62%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>46,53; 67,54</t>
+          <t>56,72; 76,22</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>57,81; 77,32</t>
+          <t>44,35; 68,25</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>55,71; 70,1</t>
+          <t>55,43; 69,84</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>75,77%</t>
+          <t>73,34%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>73,77%</t>
+          <t>75,38%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>74,77%</t>
+          <t>74,38%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>65,22; 84,53</t>
+          <t>59,74; 83,09</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>62,79; 83,42</t>
+          <t>63,25; 83,93</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>67,24; 81,4</t>
+          <t>66,28; 81,45</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>74,7%</t>
+          <t>73,78%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>74,99%</t>
+          <t>74,07%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>74,88%</t>
+          <t>73,91%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>60,4; 87,13</t>
+          <t>59,28; 84,98</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>59,44; 86,18</t>
+          <t>58,3; 85,99</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>64,82; 83,61</t>
+          <t>63,06; 82,26</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>83,73%</t>
+          <t>69,95%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>70,1%</t>
+          <t>78,45%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>77,35%</t>
+          <t>74,04%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>75,73; 92,38</t>
+          <t>58,74; 78,25</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>58,06; 78,57</t>
+          <t>70,82; 84,89</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>70,0; 85,13</t>
+          <t>67,1; 79,18</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>82,64%</t>
+          <t>80,44%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>78,43%</t>
+          <t>81,86%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>80,13%</t>
+          <t>81,01%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>72,15; 89,8</t>
+          <t>70,84; 87,5</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>68,61; 86,35</t>
+          <t>71,69; 89,96</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>72,91; 85,45</t>
+          <t>74,48; 86,38</t>
         </is>
       </c>
     </row>
@@ -799,17 +799,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>75,96%</t>
+          <t>78,97%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>80,25%</t>
+          <t>75,74%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>78,39%</t>
+          <t>77,48%</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>61,57; 87,38</t>
+          <t>64,48; 89,53</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>66,51; 89,85</t>
+          <t>59,87; 87,71</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>68,23; 85,36</t>
+          <t>67,65; 86,26</t>
         </is>
       </c>
     </row>
@@ -849,17 +849,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>76,66%</t>
+          <t>73,24%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>73,36%</t>
+          <t>73,85%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>74,89%</t>
+          <t>73,52%</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>72,17; 82,04</t>
+          <t>68,63; 77,02</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>68,38; 77,25</t>
+          <t>68,98; 77,82</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>71,54; 78,44</t>
+          <t>70,39; 76,42</t>
         </is>
       </c>
     </row>
@@ -933,12 +933,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -986,12 +986,12 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
           <t>49</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>62</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -1009,17 +1009,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>31097</t>
+          <t>46135</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>49285</t>
+          <t>31058</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>80383</t>
+          <t>77193</t>
         </is>
       </c>
     </row>
@@ -1032,17 +1032,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>25168; 36533</t>
+          <t>38899; 52277</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>41930; 56082</t>
+          <t>24254; 37323</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>70533; 88755</t>
+          <t>68326; 86098</t>
         </is>
       </c>
     </row>
@@ -1059,12 +1059,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
           <t>56</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>47</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -1082,17 +1082,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>36702</t>
+          <t>34514</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>35968</t>
+          <t>37006</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>72670</t>
+          <t>71520</t>
         </is>
       </c>
     </row>
@@ -1105,17 +1105,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>31591; 40946</t>
+          <t>28114; 39104</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>30614; 40672</t>
+          <t>31054; 41205</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>65350; 79119</t>
+          <t>63732; 78315</t>
         </is>
       </c>
     </row>
@@ -1132,12 +1132,12 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
           <t>27</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>37</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1155,17 +1155,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>18275</t>
+          <t>24157</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>28542</t>
+          <t>17859</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>46818</t>
+          <t>42015</t>
         </is>
       </c>
     </row>
@@ -1178,17 +1178,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>14776; 21316</t>
+          <t>19408; 27822</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>22623; 32798</t>
+          <t>14057; 20731</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>40525; 52275</t>
+          <t>35849; 46766</t>
         </is>
       </c>
     </row>
@@ -1205,12 +1205,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>106</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
           <t>110</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>106</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1228,17 +1228,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>100610</t>
+          <t>68304</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>74234</t>
+          <t>71228</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>174844</t>
+          <t>139532</t>
         </is>
       </c>
     </row>
@@ -1251,17 +1251,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>91000; 111003</t>
+          <t>57363; 76411</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>61482; 83199</t>
+          <t>64299; 77068</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>158244; 192435</t>
+          <t>126441; 149204</t>
         </is>
       </c>
     </row>
@@ -1278,12 +1278,12 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
           <t>65</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>78</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1301,17 +1301,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>41519</t>
+          <t>55391</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>58385</t>
+          <t>38294</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>99904</t>
+          <t>93686</t>
         </is>
       </c>
     </row>
@@ -1324,17 +1324,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>36248; 45120</t>
+          <t>48783; 60253</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>51069; 64282</t>
+          <t>33533; 42084</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>90906; 106540</t>
+          <t>86128; 99894</t>
         </is>
       </c>
     </row>
@@ -1351,12 +1351,12 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
           <t>36</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>38</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -1374,17 +1374,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>23466</t>
+          <t>29455</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>32283</t>
+          <t>24273</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>55749</t>
+          <t>53728</t>
         </is>
       </c>
     </row>
@@ -1397,17 +1397,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>19021; 26994</t>
+          <t>24050; 33392</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>26758; 36145</t>
+          <t>19186; 28108</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>48530; 60707</t>
+          <t>46915; 59821</t>
         </is>
       </c>
     </row>
@@ -1424,12 +1424,12 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>368</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
           <t>343</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>368</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -1447,17 +1447,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>251670</t>
+          <t>257956</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>278698</t>
+          <t>219719</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>530367</t>
+          <t>477674</t>
         </is>
       </c>
     </row>
@@ -1470,17 +1470,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>236932; 269341</t>
+          <t>241704; 271275</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>259784; 293464</t>
+          <t>205224; 231509</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>506638; 555525</t>
+          <t>457305; 496500</t>
         </is>
       </c>
     </row>
